--- a/output/archive/Tarnovell_Group/Integration/Client_Identity/2026/Client_Identity_Bridge_v3_2026-08.xlsx
+++ b/output/archive/Tarnovell_Group/Integration/Client_Identity/2026/Client_Identity_Bridge_v3_2026-08.xlsx
@@ -443,7 +443,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -473,6 +473,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -1711,13 +1712,14 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Osterquill archive held apart until access and QA mapping are agreed (acquisition closed 01/10/2026)</t>
+          <t>Proposed Osterquill acquisition; archive mapping pending completion and access/QA agreement</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
@@ -1726,7 +1728,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1875,6 +1877,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1882,7 +1885,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1979,5 +1982,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>